--- a/FATURAMENTO BARRA DO CORDA - JULHO.xlsx
+++ b/FATURAMENTO BARRA DO CORDA - JULHO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JAIRON\BARRA DO CORDA PROJETO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A28C5B7-10FB-47AA-BE15-E4436480F4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F0848F-E553-41FB-9EFE-34AFBDE0EBD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{8F31BE80-9032-4E5A-8DBE-88CF5640D5C7}"/>
   </bookViews>
@@ -731,10 +731,10 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1004,25 +1004,25 @@
                 <c:formatCode>_-"R$"\ * #,##0_-;\-"R$"\ * #,##0_-;_-"R$"\ * "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1472.5</c:v>
+                  <c:v>1705</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>950</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1054.5</c:v>
+                  <c:v>1265</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1119.7343198693959</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1592.96</c:v>
+                  <c:v>1408</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1615.0000000000002</c:v>
+                  <c:v>1650</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1695.2749999999999</c:v>
+                  <c:v>1815</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2959,25 +2959,25 @@
                 <c:formatCode>_-"R$"\ * #,##0_-;\-"R$"\ * #,##0_-;_-"R$"\ * "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>3875</c:v>
+                  <c:v>3487.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2500</c:v>
+                  <c:v>2475</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2775</c:v>
+                  <c:v>2475</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2946.6692628142</c:v>
+                  <c:v>2700</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4192</c:v>
+                  <c:v>2880</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4250</c:v>
+                  <c:v>3375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4461.25</c:v>
+                  <c:v>3712.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3304,25 +3304,25 @@
                 <c:formatCode>_-"R$"\ * #,##0_-;\-"R$"\ * #,##0_-;_-"R$"\ * "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1860</c:v>
+                  <c:v>2092.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1200</c:v>
+                  <c:v>1485</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1332</c:v>
+                  <c:v>1485</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1414.401246150816</c:v>
+                  <c:v>1620</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2012.1599999999999</c:v>
+                  <c:v>1728</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2040.0000000000002</c:v>
+                  <c:v>2025</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2141.4</c:v>
+                  <c:v>2227.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3999,25 +3999,25 @@
                 <c:formatCode>_-"R$"\ * #,##0_-;\-"R$"\ * #,##0_-;_-"R$"\ * "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>135.625</c:v>
+                  <c:v>155</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.5</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>97.125</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>103.133424198497</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>146.72</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>148.75</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>156.14375000000001</c:v>
+                  <c:v>165</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20733,14 +20733,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="E1" s="73" t="s">
+      <c r="C1" s="72"/>
+      <c r="E1" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="73"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
@@ -21007,12 +21007,12 @@
     <row r="11" spans="2:24" ht="21" x14ac:dyDescent="0.35">
       <c r="C11" s="25"/>
       <c r="D11" s="26"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="K11" s="73" t="s">
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="K11" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="73"/>
+      <c r="L11" s="72"/>
       <c r="N11" s="74" t="s">
         <v>25</v>
       </c>
@@ -21021,10 +21021,10 @@
       <c r="Q11" s="74"/>
     </row>
     <row r="12" spans="2:24" ht="21" x14ac:dyDescent="0.35">
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="73"/>
+      <c r="C12" s="72"/>
       <c r="G12" s="23"/>
       <c r="H12" s="24"/>
       <c r="K12" s="23" t="s">
@@ -21183,12 +21183,12 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="73" t="s">
+      <c r="B18" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
@@ -21328,12 +21328,12 @@
         <f>G22+J22</f>
         <v>23086.591</v>
       </c>
-      <c r="M22" s="73" t="s">
+      <c r="M22" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="N22" s="73"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="73"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="23" t="s">
@@ -21520,12 +21520,12 @@
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
       <c r="M30" s="45" t="s">
         <v>21</v>
       </c>
@@ -21646,10 +21646,10 @@
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="73" t="s">
+      <c r="B37" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="73"/>
+      <c r="C37" s="72"/>
       <c r="D37" s="23"/>
       <c r="E37" s="23"/>
     </row>
@@ -21713,10 +21713,10 @@
       </c>
     </row>
     <row r="44" spans="2:13" ht="24" x14ac:dyDescent="0.4">
-      <c r="B44" s="72" t="s">
+      <c r="B44" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="72"/>
+      <c r="C44" s="73"/>
     </row>
     <row r="45" spans="2:13" ht="24" x14ac:dyDescent="0.4">
       <c r="B45" s="67" t="s">
@@ -21725,10 +21725,10 @@
       <c r="C45" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="L45" s="72" t="s">
+      <c r="L45" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="M45" s="72"/>
+      <c r="M45" s="73"/>
     </row>
     <row r="46" spans="2:13" ht="24" x14ac:dyDescent="0.4">
       <c r="B46" s="68" t="s">
@@ -21796,6 +21796,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="N11:Q11"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B1:C1"/>
@@ -21803,11 +21808,6 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="N11:Q11"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21831,7 +21831,7 @@
         <v>28</v>
       </c>
       <c r="B1" s="7">
-        <v>38000</v>
+        <v>44000</v>
       </c>
       <c r="C1" s="75" t="s">
         <v>6</v>
@@ -21861,22 +21861,22 @@
         <v>0.155</v>
       </c>
       <c r="C2" s="8">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="D2" s="8">
-        <v>0.111</v>
+        <v>0.115</v>
       </c>
       <c r="E2" s="8">
-        <v>0.117866770512568</v>
+        <v>0.15</v>
       </c>
       <c r="F2" s="8">
-        <v>0.16768</v>
+        <v>0.16</v>
       </c>
       <c r="G2" s="8">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H2" s="8">
-        <v>0.17845</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="N2" t="s">
         <v>13</v>
@@ -21940,31 +21940,31 @@
       <c r="A4" s="10"/>
       <c r="B4" s="11">
         <f>$B$1*B2</f>
-        <v>5890</v>
+        <v>6820</v>
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:H4" si="2">$B$1*C2</f>
-        <v>3800</v>
+        <v>4620</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="2"/>
-        <v>4218</v>
+        <v>5060</v>
       </c>
       <c r="E4" s="11">
         <f t="shared" si="2"/>
-        <v>4478.9372794775836</v>
+        <v>6600</v>
       </c>
       <c r="F4" s="11">
         <f t="shared" si="2"/>
-        <v>6371.84</v>
+        <v>7040</v>
       </c>
       <c r="G4" s="11">
         <f t="shared" si="2"/>
-        <v>6460.0000000000009</v>
+        <v>6600</v>
       </c>
       <c r="H4" s="11">
         <f t="shared" si="2"/>
-        <v>6781.0999999999995</v>
+        <v>7260</v>
       </c>
       <c r="N4" t="s">
         <v>11</v>
@@ -21999,10 +21999,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="12">
         <v>4</v>
@@ -22019,26 +22019,20 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
-      <c r="B6" s="14">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14">
         <v>1</v>
       </c>
-      <c r="C6" s="14">
+      <c r="F6" s="14">
         <v>2</v>
       </c>
-      <c r="D6" s="14">
+      <c r="G6" s="14">
         <v>3</v>
       </c>
-      <c r="E6" s="14">
+      <c r="H6" s="14">
         <v>4</v>
-      </c>
-      <c r="F6" s="14">
-        <v>5</v>
-      </c>
-      <c r="G6" s="14">
-        <v>6</v>
-      </c>
-      <c r="H6" s="14">
-        <v>7</v>
       </c>
       <c r="X6" s="17" t="s">
         <v>14</v>
@@ -22051,33 +22045,24 @@
       <c r="A7" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="13">
-        <f t="shared" ref="B7:E7" si="3">B4/B5</f>
-        <v>1472.5</v>
-      </c>
-      <c r="C7" s="13">
-        <f t="shared" si="3"/>
-        <v>950</v>
-      </c>
-      <c r="D7" s="13">
-        <f t="shared" si="3"/>
-        <v>1054.5</v>
-      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
       <c r="E7" s="13">
-        <f t="shared" si="3"/>
-        <v>1119.7343198693959</v>
+        <f t="shared" ref="E7" si="3">E4/E5</f>
+        <v>1320</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" ref="F7:H7" si="4">F4/F5</f>
-        <v>1592.96</v>
+        <v>1408</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="4"/>
-        <v>1615.0000000000002</v>
+        <v>1650</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="4"/>
-        <v>1695.2749999999999</v>
+        <v>1815</v>
       </c>
       <c r="X7" s="17" t="s">
         <v>11</v>
@@ -22089,25 +22074,25 @@
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="78"/>
       <c r="B8" s="14">
+        <v>5</v>
+      </c>
+      <c r="C8" s="14">
+        <v>6</v>
+      </c>
+      <c r="D8" s="14">
+        <v>7</v>
+      </c>
+      <c r="E8" s="14">
         <v>8</v>
       </c>
-      <c r="C8" s="14">
+      <c r="F8" s="14">
         <v>9</v>
       </c>
-      <c r="D8" s="14">
+      <c r="G8" s="14">
         <v>10</v>
       </c>
-      <c r="E8" s="14">
+      <c r="H8" s="14">
         <v>11</v>
-      </c>
-      <c r="F8" s="14">
-        <v>12</v>
-      </c>
-      <c r="G8" s="14">
-        <v>13</v>
-      </c>
-      <c r="H8" s="14">
-        <v>14</v>
       </c>
       <c r="X8" s="19" t="s">
         <v>23</v>
@@ -22123,31 +22108,31 @@
       </c>
       <c r="B9" s="11">
         <f>B4/B5</f>
-        <v>1472.5</v>
+        <v>1705</v>
       </c>
       <c r="C9" s="11">
         <f t="shared" ref="C9" si="5">C4/C5</f>
-        <v>950</v>
+        <v>1155</v>
       </c>
       <c r="D9" s="11">
         <f>D4/D5</f>
-        <v>1054.5</v>
+        <v>1265</v>
       </c>
       <c r="E9" s="11">
         <f t="shared" ref="E9:H9" si="6">E4/E5</f>
-        <v>1119.7343198693959</v>
+        <v>1320</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="6"/>
-        <v>1592.96</v>
+        <v>1408</v>
       </c>
       <c r="G9" s="11">
         <f t="shared" si="6"/>
-        <v>1615.0000000000002</v>
+        <v>1650</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="6"/>
-        <v>1695.2749999999999</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -22155,25 +22140,25 @@
         <v>41</v>
       </c>
       <c r="B10" s="14">
+        <v>12</v>
+      </c>
+      <c r="C10" s="14">
+        <v>13</v>
+      </c>
+      <c r="D10" s="14">
+        <v>14</v>
+      </c>
+      <c r="E10" s="14">
         <v>15</v>
       </c>
-      <c r="C10" s="14">
+      <c r="F10" s="14">
         <v>16</v>
       </c>
-      <c r="D10" s="14">
+      <c r="G10" s="14">
         <v>17</v>
       </c>
-      <c r="E10" s="14">
+      <c r="H10" s="14">
         <v>18</v>
-      </c>
-      <c r="F10" s="14">
-        <v>19</v>
-      </c>
-      <c r="G10" s="14">
-        <v>20</v>
-      </c>
-      <c r="H10" s="14">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -22182,31 +22167,31 @@
       </c>
       <c r="B11" s="11">
         <f t="shared" ref="B11" si="7">B4/B5</f>
-        <v>1472.5</v>
+        <v>1705</v>
       </c>
       <c r="C11" s="11">
         <f>C4/C5</f>
-        <v>950</v>
+        <v>1155</v>
       </c>
       <c r="D11" s="11">
         <f t="shared" ref="D11:E11" si="8">D4/D5</f>
-        <v>1054.5</v>
+        <v>1265</v>
       </c>
       <c r="E11" s="11">
         <f t="shared" si="8"/>
-        <v>1119.7343198693959</v>
+        <v>1320</v>
       </c>
       <c r="F11" s="11">
         <f>F4/F5</f>
-        <v>1592.96</v>
+        <v>1408</v>
       </c>
       <c r="G11" s="11">
         <f t="shared" ref="G11" si="9">G4/G5</f>
-        <v>1615.0000000000002</v>
+        <v>1650</v>
       </c>
       <c r="H11" s="11">
         <f>H4/H5</f>
-        <v>1695.2749999999999</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -22214,25 +22199,25 @@
         <v>41</v>
       </c>
       <c r="B12" s="14">
+        <v>19</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>21</v>
+      </c>
+      <c r="E12" s="14">
         <v>22</v>
       </c>
-      <c r="C12" s="14">
+      <c r="F12" s="14">
         <v>23</v>
       </c>
-      <c r="D12" s="14">
+      <c r="G12" s="14">
         <v>24</v>
       </c>
-      <c r="E12" s="14">
+      <c r="H12" s="14">
         <v>25</v>
-      </c>
-      <c r="F12" s="14">
-        <v>26</v>
-      </c>
-      <c r="G12" s="14">
-        <v>27</v>
-      </c>
-      <c r="H12" s="14">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -22241,42 +22226,52 @@
       </c>
       <c r="B13" s="11">
         <f>B4/B5</f>
-        <v>1472.5</v>
+        <v>1705</v>
       </c>
       <c r="C13" s="11">
         <f t="shared" ref="C13" si="10">C4/C5</f>
-        <v>950</v>
+        <v>1155</v>
       </c>
       <c r="D13" s="11">
         <f>D4/D5</f>
-        <v>1054.5</v>
+        <v>1265</v>
       </c>
       <c r="E13" s="11">
         <f t="shared" ref="E13:H13" si="11">E4/E5</f>
-        <v>1119.7343198693959</v>
+        <v>1320</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="11"/>
-        <v>1592.96</v>
+        <v>1408</v>
       </c>
       <c r="G13" s="11">
         <f t="shared" si="11"/>
-        <v>1615.0000000000002</v>
+        <v>1650</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="11"/>
-        <v>1695.2749999999999</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="B14" s="14">
+        <v>26</v>
+      </c>
+      <c r="C14" s="14">
+        <v>27</v>
+      </c>
+      <c r="D14" s="14">
+        <v>28</v>
+      </c>
+      <c r="E14" s="14">
+        <v>29</v>
+      </c>
+      <c r="F14" s="14">
+        <v>30</v>
+      </c>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
     </row>
@@ -22284,11 +22279,26 @@
       <c r="A15" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="B15" s="11">
+        <f>B4/B5</f>
+        <v>1705</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" ref="C15:F15" si="12">C4/C5</f>
+        <v>1155</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="12"/>
+        <v>1265</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="12"/>
+        <v>1320</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="12"/>
+        <v>1408</v>
+      </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
     </row>
@@ -22311,25 +22321,25 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="K17">
-        <v>1472.5</v>
+        <v>1705</v>
       </c>
       <c r="L17">
-        <v>950</v>
+        <v>1155</v>
       </c>
       <c r="M17">
-        <v>1054.5</v>
+        <v>1265</v>
       </c>
       <c r="N17">
-        <v>1119.7343198693959</v>
+        <v>1320</v>
       </c>
       <c r="O17">
-        <v>1592.96</v>
+        <v>1408</v>
       </c>
       <c r="P17">
-        <v>1615.0000000000002</v>
+        <v>1650</v>
       </c>
       <c r="Q17">
-        <v>1695.2749999999999</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -22338,7 +22348,7 @@
       </c>
       <c r="B18" s="7">
         <f>SUM(B7:H7,B9:H9,B11:H11,B13:H13,B15:H15,B17:C17)</f>
-        <v>37999.877279477587</v>
+        <v>44000</v>
       </c>
       <c r="F18" s="1"/>
     </row>
@@ -22347,7 +22357,7 @@
         <v>28</v>
       </c>
       <c r="B20" s="7">
-        <v>100000</v>
+        <v>90000</v>
       </c>
       <c r="C20" s="75" t="s">
         <v>13</v>
@@ -22363,22 +22373,22 @@
         <v>0.155</v>
       </c>
       <c r="C21" s="8">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D21" s="8">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="E21" s="8">
-        <v>0.117866770512568</v>
+        <v>0.15</v>
       </c>
       <c r="F21" s="8">
-        <v>0.16768</v>
+        <v>0.16</v>
       </c>
       <c r="G21" s="8">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H21" s="8">
-        <v>0.17845</v>
+        <v>0.16500000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -22408,31 +22418,31 @@
       <c r="A23" s="10"/>
       <c r="B23" s="11">
         <f>$B$20*B21</f>
-        <v>15500</v>
+        <v>13950</v>
       </c>
       <c r="C23" s="11">
-        <f t="shared" ref="C23:D23" si="12">$B$20*C21</f>
-        <v>10000</v>
+        <f t="shared" ref="C23:D23" si="13">$B$20*C21</f>
+        <v>9900</v>
       </c>
       <c r="D23" s="11">
-        <f t="shared" si="12"/>
-        <v>11100</v>
+        <f t="shared" si="13"/>
+        <v>9900</v>
       </c>
       <c r="E23" s="11">
         <f>$B$20*E21</f>
-        <v>11786.6770512568</v>
+        <v>13500</v>
       </c>
       <c r="F23" s="11">
         <f>$B$20*F21</f>
-        <v>16768</v>
+        <v>14400</v>
       </c>
       <c r="G23" s="11">
         <f>$B$20*G21</f>
-        <v>17000</v>
+        <v>13500</v>
       </c>
       <c r="H23" s="11">
         <f>$B$20*H21</f>
-        <v>17845</v>
+        <v>14850</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -22447,10 +22457,10 @@
         <v>4</v>
       </c>
       <c r="E24" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="12">
         <v>4</v>
@@ -22461,83 +22471,68 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
-      <c r="B25" s="14">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14">
         <v>1</v>
       </c>
-      <c r="C25" s="14">
+      <c r="F25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="14">
+      <c r="G25" s="14">
         <v>3</v>
       </c>
-      <c r="E25" s="14">
+      <c r="H25" s="14">
         <v>4</v>
-      </c>
-      <c r="F25" s="14">
-        <v>5</v>
-      </c>
-      <c r="G25" s="14">
-        <v>6</v>
-      </c>
-      <c r="H25" s="14">
-        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="13">
-        <f t="shared" ref="B26:H26" si="13">B23/B24</f>
-        <v>3875</v>
-      </c>
-      <c r="C26" s="13">
-        <f t="shared" si="13"/>
-        <v>2500</v>
-      </c>
-      <c r="D26" s="13">
-        <f t="shared" si="13"/>
-        <v>2775</v>
-      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
       <c r="E26" s="13">
-        <f t="shared" si="13"/>
-        <v>2946.6692628142</v>
+        <f t="shared" ref="E26:H26" si="14">E23/E24</f>
+        <v>2700</v>
       </c>
       <c r="F26" s="13">
-        <f t="shared" si="13"/>
-        <v>4192</v>
+        <f t="shared" si="14"/>
+        <v>2880</v>
       </c>
       <c r="G26" s="13">
-        <f t="shared" si="13"/>
-        <v>4250</v>
+        <f t="shared" si="14"/>
+        <v>3375</v>
       </c>
       <c r="H26" s="13">
-        <f t="shared" si="13"/>
-        <v>4461.25</v>
+        <f t="shared" si="14"/>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="78"/>
       <c r="B27" s="14">
+        <v>5</v>
+      </c>
+      <c r="C27" s="14">
+        <v>6</v>
+      </c>
+      <c r="D27" s="14">
+        <v>7</v>
+      </c>
+      <c r="E27" s="14">
         <v>8</v>
       </c>
-      <c r="C27" s="14">
+      <c r="F27" s="14">
         <v>9</v>
       </c>
-      <c r="D27" s="14">
+      <c r="G27" s="14">
         <v>10</v>
       </c>
-      <c r="E27" s="14">
+      <c r="H27" s="14">
         <v>11</v>
-      </c>
-      <c r="F27" s="14">
-        <v>12</v>
-      </c>
-      <c r="G27" s="14">
-        <v>13</v>
-      </c>
-      <c r="H27" s="14">
-        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -22546,31 +22541,31 @@
       </c>
       <c r="B28" s="11">
         <f>B23/B24</f>
-        <v>3875</v>
+        <v>3487.5</v>
       </c>
       <c r="C28" s="11">
-        <f t="shared" ref="C28" si="14">C23/C24</f>
-        <v>2500</v>
+        <f t="shared" ref="C28" si="15">C23/C24</f>
+        <v>2475</v>
       </c>
       <c r="D28" s="11">
         <f>D23/D24</f>
-        <v>2775</v>
+        <v>2475</v>
       </c>
       <c r="E28" s="11">
-        <f t="shared" ref="E28:H28" si="15">E23/E24</f>
-        <v>2946.6692628142</v>
+        <f t="shared" ref="E28:H28" si="16">E23/E24</f>
+        <v>2700</v>
       </c>
       <c r="F28" s="11">
-        <f t="shared" si="15"/>
-        <v>4192</v>
+        <f t="shared" si="16"/>
+        <v>2880</v>
       </c>
       <c r="G28" s="11">
-        <f t="shared" si="15"/>
-        <v>4250</v>
+        <f t="shared" si="16"/>
+        <v>3375</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" si="15"/>
-        <v>4461.25</v>
+        <f t="shared" si="16"/>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -22578,25 +22573,25 @@
         <v>41</v>
       </c>
       <c r="B29" s="14">
+        <v>12</v>
+      </c>
+      <c r="C29" s="14">
+        <v>13</v>
+      </c>
+      <c r="D29" s="14">
+        <v>14</v>
+      </c>
+      <c r="E29" s="14">
         <v>15</v>
       </c>
-      <c r="C29" s="14">
+      <c r="F29" s="14">
         <v>16</v>
       </c>
-      <c r="D29" s="14">
+      <c r="G29" s="14">
         <v>17</v>
       </c>
-      <c r="E29" s="14">
+      <c r="H29" s="14">
         <v>18</v>
-      </c>
-      <c r="F29" s="14">
-        <v>19</v>
-      </c>
-      <c r="G29" s="14">
-        <v>20</v>
-      </c>
-      <c r="H29" s="14">
-        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -22604,32 +22599,32 @@
         <v>28</v>
       </c>
       <c r="B30" s="11">
-        <f t="shared" ref="B30" si="16">B23/B24</f>
-        <v>3875</v>
+        <f t="shared" ref="B30" si="17">B23/B24</f>
+        <v>3487.5</v>
       </c>
       <c r="C30" s="11">
         <f>C23/C24</f>
-        <v>2500</v>
+        <v>2475</v>
       </c>
       <c r="D30" s="11">
-        <f t="shared" ref="D30:E30" si="17">D23/D24</f>
-        <v>2775</v>
+        <f t="shared" ref="D30:E30" si="18">D23/D24</f>
+        <v>2475</v>
       </c>
       <c r="E30" s="11">
-        <f t="shared" si="17"/>
-        <v>2946.6692628142</v>
+        <f t="shared" si="18"/>
+        <v>2700</v>
       </c>
       <c r="F30" s="11">
         <f>F23/F24</f>
-        <v>4192</v>
+        <v>2880</v>
       </c>
       <c r="G30" s="11">
-        <f t="shared" ref="G30" si="18">G23/G24</f>
-        <v>4250</v>
+        <f t="shared" ref="G30" si="19">G23/G24</f>
+        <v>3375</v>
       </c>
       <c r="H30" s="11">
         <f>H23/H24</f>
-        <v>4461.25</v>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -22637,25 +22632,25 @@
         <v>41</v>
       </c>
       <c r="B31" s="14">
+        <v>19</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>21</v>
+      </c>
+      <c r="E31" s="14">
         <v>22</v>
       </c>
-      <c r="C31" s="14">
+      <c r="F31" s="14">
         <v>23</v>
       </c>
-      <c r="D31" s="14">
+      <c r="G31" s="14">
         <v>24</v>
       </c>
-      <c r="E31" s="14">
+      <c r="H31" s="14">
         <v>25</v>
-      </c>
-      <c r="F31" s="14">
-        <v>26</v>
-      </c>
-      <c r="G31" s="14">
-        <v>27</v>
-      </c>
-      <c r="H31" s="14">
-        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -22664,42 +22659,52 @@
       </c>
       <c r="B32" s="11">
         <f>B23/B24</f>
-        <v>3875</v>
+        <v>3487.5</v>
       </c>
       <c r="C32" s="11">
-        <f t="shared" ref="C32" si="19">C23/C24</f>
-        <v>2500</v>
+        <f t="shared" ref="C32" si="20">C23/C24</f>
+        <v>2475</v>
       </c>
       <c r="D32" s="11">
         <f>D23/D24</f>
-        <v>2775</v>
+        <v>2475</v>
       </c>
       <c r="E32" s="11">
-        <f t="shared" ref="E32:H32" si="20">E23/E24</f>
-        <v>2946.6692628142</v>
+        <f t="shared" ref="E32:H32" si="21">E23/E24</f>
+        <v>2700</v>
       </c>
       <c r="F32" s="11">
-        <f t="shared" si="20"/>
-        <v>4192</v>
+        <f t="shared" si="21"/>
+        <v>2880</v>
       </c>
       <c r="G32" s="11">
-        <f t="shared" si="20"/>
-        <v>4250</v>
+        <f t="shared" si="21"/>
+        <v>3375</v>
       </c>
       <c r="H32" s="11">
-        <f t="shared" si="20"/>
-        <v>4461.25</v>
+        <f t="shared" si="21"/>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="B33" s="14">
+        <v>26</v>
+      </c>
+      <c r="C33" s="14">
+        <v>27</v>
+      </c>
+      <c r="D33" s="14">
+        <v>28</v>
+      </c>
+      <c r="E33" s="14">
+        <v>29</v>
+      </c>
+      <c r="F33" s="14">
+        <v>30</v>
+      </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
     </row>
@@ -22707,11 +22712,26 @@
       <c r="A34" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
+      <c r="B34" s="11">
+        <f>B23/B24</f>
+        <v>3487.5</v>
+      </c>
+      <c r="C34" s="11">
+        <f t="shared" ref="C34:F34" si="22">C23/C24</f>
+        <v>2475</v>
+      </c>
+      <c r="D34" s="11">
+        <f t="shared" si="22"/>
+        <v>2475</v>
+      </c>
+      <c r="E34" s="11">
+        <f t="shared" si="22"/>
+        <v>2700</v>
+      </c>
+      <c r="F34" s="11">
+        <f t="shared" si="22"/>
+        <v>2880</v>
+      </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
     </row>
@@ -22734,25 +22754,25 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="L36">
-        <v>3875</v>
+        <v>3487.5</v>
       </c>
       <c r="M36">
-        <v>2500</v>
+        <v>2475</v>
       </c>
       <c r="N36">
-        <v>2775</v>
+        <v>2475</v>
       </c>
       <c r="O36">
-        <v>2946.6692628142</v>
+        <v>2700</v>
       </c>
       <c r="P36">
-        <v>4192</v>
+        <v>2880</v>
       </c>
       <c r="Q36">
-        <v>4250</v>
+        <v>3375</v>
       </c>
       <c r="R36">
-        <v>4461.25</v>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -22761,7 +22781,7 @@
       </c>
       <c r="B37" s="7">
         <f>SUM(B26:H26,B28:H28,B30:H30,B32:H32,B34:H34,B36:C36)</f>
-        <v>99999.677051256804</v>
+        <v>90000</v>
       </c>
       <c r="F37" s="1"/>
     </row>
@@ -22770,7 +22790,7 @@
         <v>28</v>
       </c>
       <c r="B39" s="7">
-        <v>48000</v>
+        <v>54000</v>
       </c>
       <c r="C39" s="75" t="s">
         <v>14</v>
@@ -22786,22 +22806,22 @@
         <v>0.155</v>
       </c>
       <c r="C40" s="8">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D40" s="8">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="E40" s="8">
-        <v>0.117866770512568</v>
+        <v>0.15</v>
       </c>
       <c r="F40" s="8">
-        <v>0.16768</v>
+        <v>0.16</v>
       </c>
       <c r="G40" s="8">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H40" s="8">
-        <v>0.17845</v>
+        <v>0.16500000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -22831,31 +22851,31 @@
       <c r="A42" s="10"/>
       <c r="B42" s="11">
         <f>$B$39*B40</f>
-        <v>7440</v>
+        <v>8370</v>
       </c>
       <c r="C42" s="11">
-        <f t="shared" ref="C42:H42" si="21">$B$39*C40</f>
-        <v>4800</v>
+        <f t="shared" ref="C42:H42" si="23">$B$39*C40</f>
+        <v>5940</v>
       </c>
       <c r="D42" s="11">
-        <f t="shared" si="21"/>
-        <v>5328</v>
+        <f t="shared" si="23"/>
+        <v>5940</v>
       </c>
       <c r="E42" s="11">
-        <f t="shared" si="21"/>
-        <v>5657.6049846032638</v>
+        <f t="shared" si="23"/>
+        <v>8100</v>
       </c>
       <c r="F42" s="11">
-        <f t="shared" si="21"/>
-        <v>8048.6399999999994</v>
+        <f t="shared" si="23"/>
+        <v>8640</v>
       </c>
       <c r="G42" s="11">
-        <f t="shared" si="21"/>
-        <v>8160.0000000000009</v>
+        <f t="shared" si="23"/>
+        <v>8100</v>
       </c>
       <c r="H42" s="11">
-        <f t="shared" si="21"/>
-        <v>8565.6</v>
+        <f t="shared" si="23"/>
+        <v>8910</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -22870,10 +22890,10 @@
         <v>4</v>
       </c>
       <c r="E43" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43" s="12">
         <v>4</v>
@@ -22884,83 +22904,68 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="14">
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14">
         <v>1</v>
       </c>
-      <c r="C44" s="14">
+      <c r="F44" s="14">
         <v>2</v>
       </c>
-      <c r="D44" s="14">
+      <c r="G44" s="14">
         <v>3</v>
       </c>
-      <c r="E44" s="14">
+      <c r="H44" s="14">
         <v>4</v>
-      </c>
-      <c r="F44" s="14">
-        <v>5</v>
-      </c>
-      <c r="G44" s="14">
-        <v>6</v>
-      </c>
-      <c r="H44" s="14">
-        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="13">
-        <f t="shared" ref="B45:H45" si="22">B42/B43</f>
-        <v>1860</v>
-      </c>
-      <c r="C45" s="13">
-        <f t="shared" si="22"/>
-        <v>1200</v>
-      </c>
-      <c r="D45" s="13">
-        <f t="shared" si="22"/>
-        <v>1332</v>
-      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
       <c r="E45" s="13">
-        <f t="shared" si="22"/>
-        <v>1414.401246150816</v>
+        <f t="shared" ref="E45:H45" si="24">E42/E43</f>
+        <v>1620</v>
       </c>
       <c r="F45" s="13">
-        <f t="shared" si="22"/>
-        <v>2012.1599999999999</v>
+        <f t="shared" si="24"/>
+        <v>1728</v>
       </c>
       <c r="G45" s="13">
-        <f t="shared" si="22"/>
-        <v>2040.0000000000002</v>
+        <f t="shared" si="24"/>
+        <v>2025</v>
       </c>
       <c r="H45" s="13">
-        <f t="shared" si="22"/>
-        <v>2141.4</v>
+        <f t="shared" si="24"/>
+        <v>2227.5</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="78"/>
       <c r="B46" s="14">
+        <v>5</v>
+      </c>
+      <c r="C46" s="14">
+        <v>6</v>
+      </c>
+      <c r="D46" s="14">
+        <v>7</v>
+      </c>
+      <c r="E46" s="14">
         <v>8</v>
       </c>
-      <c r="C46" s="14">
+      <c r="F46" s="14">
         <v>9</v>
       </c>
-      <c r="D46" s="14">
+      <c r="G46" s="14">
         <v>10</v>
       </c>
-      <c r="E46" s="14">
+      <c r="H46" s="14">
         <v>11</v>
-      </c>
-      <c r="F46" s="14">
-        <v>12</v>
-      </c>
-      <c r="G46" s="14">
-        <v>13</v>
-      </c>
-      <c r="H46" s="14">
-        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -22969,31 +22974,31 @@
       </c>
       <c r="B47" s="11">
         <f>B42/B43</f>
-        <v>1860</v>
+        <v>2092.5</v>
       </c>
       <c r="C47" s="11">
-        <f t="shared" ref="C47" si="23">C42/C43</f>
-        <v>1200</v>
+        <f t="shared" ref="C47" si="25">C42/C43</f>
+        <v>1485</v>
       </c>
       <c r="D47" s="11">
         <f>D42/D43</f>
-        <v>1332</v>
+        <v>1485</v>
       </c>
       <c r="E47" s="11">
-        <f t="shared" ref="E47:H47" si="24">E42/E43</f>
-        <v>1414.401246150816</v>
+        <f t="shared" ref="E47:H47" si="26">E42/E43</f>
+        <v>1620</v>
       </c>
       <c r="F47" s="11">
-        <f t="shared" si="24"/>
-        <v>2012.1599999999999</v>
+        <f t="shared" si="26"/>
+        <v>1728</v>
       </c>
       <c r="G47" s="11">
-        <f t="shared" si="24"/>
-        <v>2040.0000000000002</v>
+        <f t="shared" si="26"/>
+        <v>2025</v>
       </c>
       <c r="H47" s="11">
-        <f t="shared" si="24"/>
-        <v>2141.4</v>
+        <f t="shared" si="26"/>
+        <v>2227.5</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -23001,25 +23006,25 @@
         <v>41</v>
       </c>
       <c r="B48" s="14">
+        <v>12</v>
+      </c>
+      <c r="C48" s="14">
+        <v>13</v>
+      </c>
+      <c r="D48" s="14">
+        <v>14</v>
+      </c>
+      <c r="E48" s="14">
         <v>15</v>
       </c>
-      <c r="C48" s="14">
+      <c r="F48" s="14">
         <v>16</v>
       </c>
-      <c r="D48" s="14">
+      <c r="G48" s="14">
         <v>17</v>
       </c>
-      <c r="E48" s="14">
+      <c r="H48" s="14">
         <v>18</v>
-      </c>
-      <c r="F48" s="14">
-        <v>19</v>
-      </c>
-      <c r="G48" s="14">
-        <v>20</v>
-      </c>
-      <c r="H48" s="14">
-        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -23027,32 +23032,32 @@
         <v>28</v>
       </c>
       <c r="B49" s="11">
-        <f t="shared" ref="B49" si="25">B42/B43</f>
-        <v>1860</v>
+        <f t="shared" ref="B49" si="27">B42/B43</f>
+        <v>2092.5</v>
       </c>
       <c r="C49" s="11">
         <f>C42/C43</f>
-        <v>1200</v>
+        <v>1485</v>
       </c>
       <c r="D49" s="11">
-        <f t="shared" ref="D49:E49" si="26">D42/D43</f>
-        <v>1332</v>
+        <f t="shared" ref="D49:E49" si="28">D42/D43</f>
+        <v>1485</v>
       </c>
       <c r="E49" s="11">
-        <f t="shared" si="26"/>
-        <v>1414.401246150816</v>
+        <f t="shared" si="28"/>
+        <v>1620</v>
       </c>
       <c r="F49" s="11">
         <f>F42/F43</f>
-        <v>2012.1599999999999</v>
+        <v>1728</v>
       </c>
       <c r="G49" s="11">
-        <f t="shared" ref="G49" si="27">G42/G43</f>
-        <v>2040.0000000000002</v>
+        <f t="shared" ref="G49" si="29">G42/G43</f>
+        <v>2025</v>
       </c>
       <c r="H49" s="11">
         <f>H42/H43</f>
-        <v>2141.4</v>
+        <v>2227.5</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -23060,25 +23065,25 @@
         <v>41</v>
       </c>
       <c r="B50" s="14">
+        <v>19</v>
+      </c>
+      <c r="C50" s="14">
+        <v>20</v>
+      </c>
+      <c r="D50" s="14">
+        <v>21</v>
+      </c>
+      <c r="E50" s="14">
         <v>22</v>
       </c>
-      <c r="C50" s="14">
+      <c r="F50" s="14">
         <v>23</v>
       </c>
-      <c r="D50" s="14">
+      <c r="G50" s="14">
         <v>24</v>
       </c>
-      <c r="E50" s="14">
+      <c r="H50" s="14">
         <v>25</v>
-      </c>
-      <c r="F50" s="14">
-        <v>26</v>
-      </c>
-      <c r="G50" s="14">
-        <v>27</v>
-      </c>
-      <c r="H50" s="14">
-        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -23087,42 +23092,52 @@
       </c>
       <c r="B51" s="11">
         <f>B42/B43</f>
-        <v>1860</v>
+        <v>2092.5</v>
       </c>
       <c r="C51" s="11">
-        <f t="shared" ref="C51" si="28">C42/C43</f>
-        <v>1200</v>
+        <f t="shared" ref="C51" si="30">C42/C43</f>
+        <v>1485</v>
       </c>
       <c r="D51" s="11">
         <f>D42/D43</f>
-        <v>1332</v>
+        <v>1485</v>
       </c>
       <c r="E51" s="11">
-        <f t="shared" ref="E51:H51" si="29">E42/E43</f>
-        <v>1414.401246150816</v>
+        <f t="shared" ref="E51:H51" si="31">E42/E43</f>
+        <v>1620</v>
       </c>
       <c r="F51" s="11">
-        <f t="shared" si="29"/>
-        <v>2012.1599999999999</v>
+        <f t="shared" si="31"/>
+        <v>1728</v>
       </c>
       <c r="G51" s="11">
-        <f t="shared" si="29"/>
-        <v>2040.0000000000002</v>
+        <f t="shared" si="31"/>
+        <v>2025</v>
       </c>
       <c r="H51" s="11">
-        <f t="shared" si="29"/>
-        <v>2141.4</v>
+        <f t="shared" si="31"/>
+        <v>2227.5</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
+      <c r="B52" s="14">
+        <v>26</v>
+      </c>
+      <c r="C52" s="14">
+        <v>27</v>
+      </c>
+      <c r="D52" s="14">
+        <v>28</v>
+      </c>
+      <c r="E52" s="14">
+        <v>29</v>
+      </c>
+      <c r="F52" s="14">
+        <v>30</v>
+      </c>
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
     </row>
@@ -23130,11 +23145,26 @@
       <c r="A53" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
+      <c r="B53" s="11">
+        <f>B42/B43</f>
+        <v>2092.5</v>
+      </c>
+      <c r="C53" s="11">
+        <f t="shared" ref="C53:F53" si="32">C42/C43</f>
+        <v>1485</v>
+      </c>
+      <c r="D53" s="11">
+        <f t="shared" si="32"/>
+        <v>1485</v>
+      </c>
+      <c r="E53" s="11">
+        <f t="shared" si="32"/>
+        <v>1620</v>
+      </c>
+      <c r="F53" s="11">
+        <f t="shared" si="32"/>
+        <v>1728</v>
+      </c>
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
     </row>
@@ -23147,25 +23177,25 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="M54">
-        <v>1860</v>
+        <v>2092.5</v>
       </c>
       <c r="N54">
-        <v>1200</v>
+        <v>1485</v>
       </c>
       <c r="O54">
-        <v>1332</v>
+        <v>1485</v>
       </c>
       <c r="P54">
-        <v>1414.401246150816</v>
+        <v>1620</v>
       </c>
       <c r="Q54">
-        <v>2012.1599999999999</v>
+        <v>1728</v>
       </c>
       <c r="R54">
-        <v>2040.0000000000002</v>
+        <v>2025</v>
       </c>
       <c r="S54">
-        <v>2141.4</v>
+        <v>2227.5</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -23184,7 +23214,7 @@
       </c>
       <c r="B56" s="7">
         <f>SUM(B45:H45,B47:H47,B49:H49,B51:H51,B53:H53,B55:C55)</f>
-        <v>47999.844984603267</v>
+        <v>54000</v>
       </c>
       <c r="F56" s="1"/>
     </row>
@@ -23257,27 +23287,27 @@
         <v>2790</v>
       </c>
       <c r="C61" s="11">
-        <f t="shared" ref="C61:H61" si="30">$B$58*C59</f>
+        <f t="shared" ref="C61:H61" si="33">$B$58*C59</f>
         <v>1800</v>
       </c>
       <c r="D61" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1998</v>
       </c>
       <c r="E61" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>2121.6018692262242</v>
       </c>
       <c r="F61" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>3018.24</v>
       </c>
       <c r="G61" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>3060</v>
       </c>
       <c r="H61" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>3212.1</v>
       </c>
     </row>
@@ -23334,31 +23364,31 @@
         <v>41</v>
       </c>
       <c r="B64" s="13">
-        <f t="shared" ref="B64:H64" si="31">B61/B62</f>
+        <f t="shared" ref="B64:H64" si="34">B61/B62</f>
         <v>697.5</v>
       </c>
       <c r="C64" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>450</v>
       </c>
       <c r="D64" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>499.5</v>
       </c>
       <c r="E64" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>530.40046730655604</v>
       </c>
       <c r="F64" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>754.56</v>
       </c>
       <c r="G64" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>765</v>
       </c>
       <c r="H64" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>803.02499999999998</v>
       </c>
     </row>
@@ -23395,7 +23425,7 @@
         <v>697.5</v>
       </c>
       <c r="C66" s="11">
-        <f t="shared" ref="C66" si="32">C61/C62</f>
+        <f t="shared" ref="C66" si="35">C61/C62</f>
         <v>450</v>
       </c>
       <c r="D66" s="11">
@@ -23403,19 +23433,19 @@
         <v>499.5</v>
       </c>
       <c r="E66" s="11">
-        <f t="shared" ref="E66:H66" si="33">E61/E62</f>
+        <f t="shared" ref="E66:H66" si="36">E61/E62</f>
         <v>530.40046730655604</v>
       </c>
       <c r="F66" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>754.56</v>
       </c>
       <c r="G66" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>765</v>
       </c>
       <c r="H66" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>803.02499999999998</v>
       </c>
     </row>
@@ -23450,7 +23480,7 @@
         <v>28</v>
       </c>
       <c r="B68" s="11">
-        <f t="shared" ref="B68" si="34">B61/B62</f>
+        <f t="shared" ref="B68" si="37">B61/B62</f>
         <v>697.5</v>
       </c>
       <c r="C68" s="11">
@@ -23458,11 +23488,11 @@
         <v>450</v>
       </c>
       <c r="D68" s="11">
-        <f t="shared" ref="D68:E68" si="35">D61/D62</f>
+        <f t="shared" ref="D68:E68" si="38">D61/D62</f>
         <v>499.5</v>
       </c>
       <c r="E68" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>530.40046730655604</v>
       </c>
       <c r="F68" s="11">
@@ -23470,7 +23500,7 @@
         <v>754.56</v>
       </c>
       <c r="G68" s="11">
-        <f t="shared" ref="G68" si="36">G61/G62</f>
+        <f t="shared" ref="G68" si="39">G61/G62</f>
         <v>765</v>
       </c>
       <c r="H68" s="11">
@@ -23513,7 +23543,7 @@
         <v>697.5</v>
       </c>
       <c r="C70" s="11">
-        <f t="shared" ref="C70" si="37">C61/C62</f>
+        <f t="shared" ref="C70" si="40">C61/C62</f>
         <v>450</v>
       </c>
       <c r="D70" s="11">
@@ -23521,19 +23551,19 @@
         <v>499.5</v>
       </c>
       <c r="E70" s="11">
-        <f t="shared" ref="E70:H70" si="38">E61/E62</f>
+        <f t="shared" ref="E70:H70" si="41">E61/E62</f>
         <v>530.40046730655604</v>
       </c>
       <c r="F70" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>754.56</v>
       </c>
       <c r="G70" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>765</v>
       </c>
       <c r="H70" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>803.02499999999998</v>
       </c>
     </row>
@@ -23616,7 +23646,7 @@
         <v>28</v>
       </c>
       <c r="B77" s="7">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="C77" s="75" t="s">
         <v>19</v>
@@ -23632,22 +23662,22 @@
         <v>0.155</v>
       </c>
       <c r="C78" s="8">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D78" s="8">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="E78" s="8">
-        <v>0.117866770512568</v>
+        <v>0.15</v>
       </c>
       <c r="F78" s="8">
-        <v>0.16768</v>
+        <v>0.16</v>
       </c>
       <c r="G78" s="8">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H78" s="8">
-        <v>0.17845</v>
+        <v>0.16500000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -23677,31 +23707,31 @@
       <c r="A80" s="10"/>
       <c r="B80" s="11">
         <f>$B$77*B78</f>
-        <v>542.5</v>
+        <v>620</v>
       </c>
       <c r="C80" s="11">
-        <f t="shared" ref="C80:H80" si="39">$B$77*C78</f>
-        <v>350</v>
+        <f t="shared" ref="C80:H80" si="42">$B$77*C78</f>
+        <v>440</v>
       </c>
       <c r="D80" s="11">
-        <f t="shared" si="39"/>
-        <v>388.5</v>
+        <f t="shared" si="42"/>
+        <v>440</v>
       </c>
       <c r="E80" s="11">
-        <f t="shared" si="39"/>
-        <v>412.53369679398799</v>
+        <f t="shared" si="42"/>
+        <v>600</v>
       </c>
       <c r="F80" s="11">
-        <f t="shared" si="39"/>
-        <v>586.88</v>
+        <f t="shared" si="42"/>
+        <v>640</v>
       </c>
       <c r="G80" s="11">
-        <f t="shared" si="39"/>
-        <v>595</v>
+        <f t="shared" si="42"/>
+        <v>600</v>
       </c>
       <c r="H80" s="11">
-        <f t="shared" si="39"/>
-        <v>624.57500000000005</v>
+        <f t="shared" si="42"/>
+        <v>660</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -23716,10 +23746,10 @@
         <v>4</v>
       </c>
       <c r="E81" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F81" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G81" s="12">
         <v>4</v>
@@ -23730,83 +23760,68 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="10"/>
-      <c r="B82" s="14">
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14">
         <v>1</v>
       </c>
-      <c r="C82" s="14">
+      <c r="F82" s="14">
         <v>2</v>
       </c>
-      <c r="D82" s="14">
+      <c r="G82" s="14">
         <v>3</v>
       </c>
-      <c r="E82" s="14">
+      <c r="H82" s="14">
         <v>4</v>
-      </c>
-      <c r="F82" s="14">
-        <v>5</v>
-      </c>
-      <c r="G82" s="14">
-        <v>6</v>
-      </c>
-      <c r="H82" s="14">
-        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B83" s="13">
-        <f t="shared" ref="B83:H83" si="40">B80/B81</f>
-        <v>135.625</v>
-      </c>
-      <c r="C83" s="13">
-        <f t="shared" si="40"/>
-        <v>87.5</v>
-      </c>
-      <c r="D83" s="13">
-        <f t="shared" si="40"/>
-        <v>97.125</v>
-      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
       <c r="E83" s="13">
-        <f t="shared" si="40"/>
-        <v>103.133424198497</v>
+        <f t="shared" ref="E83:H83" si="43">E80/E81</f>
+        <v>120</v>
       </c>
       <c r="F83" s="13">
-        <f t="shared" si="40"/>
-        <v>146.72</v>
+        <f t="shared" si="43"/>
+        <v>128</v>
       </c>
       <c r="G83" s="13">
-        <f t="shared" si="40"/>
-        <v>148.75</v>
+        <f t="shared" si="43"/>
+        <v>150</v>
       </c>
       <c r="H83" s="13">
-        <f t="shared" si="40"/>
-        <v>156.14375000000001</v>
+        <f t="shared" si="43"/>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="78"/>
       <c r="B84" s="14">
+        <v>5</v>
+      </c>
+      <c r="C84" s="14">
+        <v>6</v>
+      </c>
+      <c r="D84" s="14">
+        <v>7</v>
+      </c>
+      <c r="E84" s="14">
         <v>8</v>
       </c>
-      <c r="C84" s="14">
+      <c r="F84" s="14">
         <v>9</v>
       </c>
-      <c r="D84" s="14">
+      <c r="G84" s="14">
         <v>10</v>
       </c>
-      <c r="E84" s="14">
+      <c r="H84" s="14">
         <v>11</v>
-      </c>
-      <c r="F84" s="14">
-        <v>12</v>
-      </c>
-      <c r="G84" s="14">
-        <v>13</v>
-      </c>
-      <c r="H84" s="14">
-        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
@@ -23815,31 +23830,31 @@
       </c>
       <c r="B85" s="11">
         <f>B80/B81</f>
-        <v>135.625</v>
+        <v>155</v>
       </c>
       <c r="C85" s="11">
-        <f t="shared" ref="C85" si="41">C80/C81</f>
-        <v>87.5</v>
+        <f t="shared" ref="C85" si="44">C80/C81</f>
+        <v>110</v>
       </c>
       <c r="D85" s="11">
         <f>D80/D81</f>
-        <v>97.125</v>
+        <v>110</v>
       </c>
       <c r="E85" s="11">
-        <f t="shared" ref="E85:H85" si="42">E80/E81</f>
-        <v>103.133424198497</v>
+        <f t="shared" ref="E85:H85" si="45">E80/E81</f>
+        <v>120</v>
       </c>
       <c r="F85" s="11">
-        <f t="shared" si="42"/>
-        <v>146.72</v>
+        <f t="shared" si="45"/>
+        <v>128</v>
       </c>
       <c r="G85" s="11">
-        <f t="shared" si="42"/>
-        <v>148.75</v>
+        <f t="shared" si="45"/>
+        <v>150</v>
       </c>
       <c r="H85" s="11">
-        <f t="shared" si="42"/>
-        <v>156.14375000000001</v>
+        <f t="shared" si="45"/>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
@@ -23847,25 +23862,25 @@
         <v>41</v>
       </c>
       <c r="B86" s="14">
+        <v>12</v>
+      </c>
+      <c r="C86" s="14">
+        <v>13</v>
+      </c>
+      <c r="D86" s="14">
+        <v>14</v>
+      </c>
+      <c r="E86" s="14">
         <v>15</v>
       </c>
-      <c r="C86" s="14">
+      <c r="F86" s="14">
         <v>16</v>
       </c>
-      <c r="D86" s="14">
+      <c r="G86" s="14">
         <v>17</v>
       </c>
-      <c r="E86" s="14">
+      <c r="H86" s="14">
         <v>18</v>
-      </c>
-      <c r="F86" s="14">
-        <v>19</v>
-      </c>
-      <c r="G86" s="14">
-        <v>20</v>
-      </c>
-      <c r="H86" s="14">
-        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
@@ -23873,32 +23888,32 @@
         <v>28</v>
       </c>
       <c r="B87" s="11">
-        <f t="shared" ref="B87" si="43">B80/B81</f>
-        <v>135.625</v>
+        <f t="shared" ref="B87" si="46">B80/B81</f>
+        <v>155</v>
       </c>
       <c r="C87" s="11">
         <f>C80/C81</f>
-        <v>87.5</v>
+        <v>110</v>
       </c>
       <c r="D87" s="11">
-        <f t="shared" ref="D87:E87" si="44">D80/D81</f>
-        <v>97.125</v>
+        <f t="shared" ref="D87:E87" si="47">D80/D81</f>
+        <v>110</v>
       </c>
       <c r="E87" s="11">
-        <f t="shared" si="44"/>
-        <v>103.133424198497</v>
+        <f t="shared" si="47"/>
+        <v>120</v>
       </c>
       <c r="F87" s="11">
         <f>F80/F81</f>
-        <v>146.72</v>
+        <v>128</v>
       </c>
       <c r="G87" s="11">
-        <f t="shared" ref="G87" si="45">G80/G81</f>
-        <v>148.75</v>
+        <f t="shared" ref="G87" si="48">G80/G81</f>
+        <v>150</v>
       </c>
       <c r="H87" s="11">
         <f>H80/H81</f>
-        <v>156.14375000000001</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -23906,25 +23921,25 @@
         <v>41</v>
       </c>
       <c r="B88" s="14">
+        <v>19</v>
+      </c>
+      <c r="C88" s="14">
+        <v>20</v>
+      </c>
+      <c r="D88" s="14">
+        <v>21</v>
+      </c>
+      <c r="E88" s="14">
         <v>22</v>
       </c>
-      <c r="C88" s="14">
+      <c r="F88" s="14">
         <v>23</v>
       </c>
-      <c r="D88" s="14">
+      <c r="G88" s="14">
         <v>24</v>
       </c>
-      <c r="E88" s="14">
+      <c r="H88" s="14">
         <v>25</v>
-      </c>
-      <c r="F88" s="14">
-        <v>26</v>
-      </c>
-      <c r="G88" s="14">
-        <v>27</v>
-      </c>
-      <c r="H88" s="14">
-        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
@@ -23933,42 +23948,52 @@
       </c>
       <c r="B89" s="11">
         <f>B80/B81</f>
-        <v>135.625</v>
+        <v>155</v>
       </c>
       <c r="C89" s="11">
-        <f t="shared" ref="C89" si="46">C80/C81</f>
-        <v>87.5</v>
+        <f t="shared" ref="C89" si="49">C80/C81</f>
+        <v>110</v>
       </c>
       <c r="D89" s="11">
         <f>D80/D81</f>
-        <v>97.125</v>
+        <v>110</v>
       </c>
       <c r="E89" s="11">
-        <f t="shared" ref="E89:H89" si="47">E80/E81</f>
-        <v>103.133424198497</v>
+        <f t="shared" ref="E89:H89" si="50">E80/E81</f>
+        <v>120</v>
       </c>
       <c r="F89" s="11">
-        <f t="shared" si="47"/>
-        <v>146.72</v>
+        <f t="shared" si="50"/>
+        <v>128</v>
       </c>
       <c r="G89" s="11">
-        <f t="shared" si="47"/>
-        <v>148.75</v>
+        <f t="shared" si="50"/>
+        <v>150</v>
       </c>
       <c r="H89" s="11">
-        <f t="shared" si="47"/>
-        <v>156.14375000000001</v>
+        <f t="shared" si="50"/>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
+      <c r="B90" s="14">
+        <v>26</v>
+      </c>
+      <c r="C90" s="14">
+        <v>27</v>
+      </c>
+      <c r="D90" s="14">
+        <v>28</v>
+      </c>
+      <c r="E90" s="14">
+        <v>29</v>
+      </c>
+      <c r="F90" s="14">
+        <v>30</v>
+      </c>
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
     </row>
@@ -23976,11 +24001,26 @@
       <c r="A91" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
+      <c r="B91" s="11">
+        <f>B80/B81</f>
+        <v>155</v>
+      </c>
+      <c r="C91" s="11">
+        <f t="shared" ref="C91:F91" si="51">C80/C81</f>
+        <v>110</v>
+      </c>
+      <c r="D91" s="11">
+        <f t="shared" si="51"/>
+        <v>110</v>
+      </c>
+      <c r="E91" s="11">
+        <f t="shared" si="51"/>
+        <v>120</v>
+      </c>
+      <c r="F91" s="11">
+        <f t="shared" si="51"/>
+        <v>128</v>
+      </c>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
     </row>
@@ -24030,7 +24070,7 @@
       </c>
       <c r="B94" s="7">
         <f>SUM(B83:H83,B85:H85,B87:H87,B89:H89,B91:H91,B93:C93)</f>
-        <v>3499.9886967939879</v>
+        <v>4000</v>
       </c>
       <c r="F94" s="1"/>
     </row>
@@ -24103,27 +24143,27 @@
         <v>5735</v>
       </c>
       <c r="C99" s="11">
-        <f t="shared" ref="C99:H99" si="48">$B$96*C97</f>
+        <f t="shared" ref="C99:H99" si="52">$B$96*C97</f>
         <v>3700</v>
       </c>
       <c r="D99" s="11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>4107</v>
       </c>
       <c r="E99" s="11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>4361.0705089650155</v>
       </c>
       <c r="F99" s="11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>6204.16</v>
       </c>
       <c r="G99" s="11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>6290</v>
       </c>
       <c r="H99" s="11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>6602.65</v>
       </c>
       <c r="L99">
@@ -24201,31 +24241,31 @@
         <v>41</v>
       </c>
       <c r="B102" s="13">
-        <f t="shared" ref="B102:H102" si="49">B99/B100</f>
+        <f t="shared" ref="B102:H102" si="53">B99/B100</f>
         <v>1433.75</v>
       </c>
       <c r="C102" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>925</v>
       </c>
       <c r="D102" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1026.75</v>
       </c>
       <c r="E102" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1090.2676272412539</v>
       </c>
       <c r="F102" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1551.04</v>
       </c>
       <c r="G102" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1572.5</v>
       </c>
       <c r="H102" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>1650.6624999999999</v>
       </c>
     </row>
@@ -24262,7 +24302,7 @@
         <v>1433.75</v>
       </c>
       <c r="C104" s="11">
-        <f t="shared" ref="C104" si="50">C99/C100</f>
+        <f t="shared" ref="C104" si="54">C99/C100</f>
         <v>925</v>
       </c>
       <c r="D104" s="11">
@@ -24270,19 +24310,19 @@
         <v>1026.75</v>
       </c>
       <c r="E104" s="11">
-        <f t="shared" ref="E104:H104" si="51">E99/E100</f>
+        <f t="shared" ref="E104:H104" si="55">E99/E100</f>
         <v>1090.2676272412539</v>
       </c>
       <c r="F104" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1551.04</v>
       </c>
       <c r="G104" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1572.5</v>
       </c>
       <c r="H104" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1650.6624999999999</v>
       </c>
     </row>
@@ -24317,7 +24357,7 @@
         <v>28</v>
       </c>
       <c r="B106" s="11">
-        <f t="shared" ref="B106" si="52">B99/B100</f>
+        <f t="shared" ref="B106" si="56">B99/B100</f>
         <v>1433.75</v>
       </c>
       <c r="C106" s="11">
@@ -24325,11 +24365,11 @@
         <v>925</v>
       </c>
       <c r="D106" s="11">
-        <f t="shared" ref="D106:E106" si="53">D99/D100</f>
+        <f t="shared" ref="D106:E106" si="57">D99/D100</f>
         <v>1026.75</v>
       </c>
       <c r="E106" s="11">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>1090.2676272412539</v>
       </c>
       <c r="F106" s="11">
@@ -24337,7 +24377,7 @@
         <v>1551.04</v>
       </c>
       <c r="G106" s="11">
-        <f t="shared" ref="G106" si="54">G99/G100</f>
+        <f t="shared" ref="G106" si="58">G99/G100</f>
         <v>1572.5</v>
       </c>
       <c r="H106" s="11">
@@ -24380,7 +24420,7 @@
         <v>1433.75</v>
       </c>
       <c r="C108" s="11">
-        <f t="shared" ref="C108" si="55">C99/C100</f>
+        <f t="shared" ref="C108" si="59">C99/C100</f>
         <v>925</v>
       </c>
       <c r="D108" s="11">
@@ -24388,19 +24428,19 @@
         <v>1026.75</v>
       </c>
       <c r="E108" s="11">
-        <f t="shared" ref="E108:H108" si="56">E99/E100</f>
+        <f t="shared" ref="E108:H108" si="60">E99/E100</f>
         <v>1090.2676272412539</v>
       </c>
       <c r="F108" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>1551.04</v>
       </c>
       <c r="G108" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>1572.5</v>
       </c>
       <c r="H108" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>1650.6624999999999</v>
       </c>
     </row>
@@ -24526,27 +24566,27 @@
         <v>3565</v>
       </c>
       <c r="C118" s="11">
-        <f t="shared" ref="C118:H118" si="57">$B$115*C116</f>
+        <f t="shared" ref="C118:H118" si="61">$B$115*C116</f>
         <v>2300</v>
       </c>
       <c r="D118" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>2553</v>
       </c>
       <c r="E118" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>2710.9357217890638</v>
       </c>
       <c r="F118" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>3856.64</v>
       </c>
       <c r="G118" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>3910.0000000000005</v>
       </c>
       <c r="H118" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4104.3500000000004</v>
       </c>
     </row>
@@ -24603,31 +24643,31 @@
         <v>41</v>
       </c>
       <c r="B121" s="13">
-        <f t="shared" ref="B121:H121" si="58">B118/B119</f>
+        <f t="shared" ref="B121:H121" si="62">B118/B119</f>
         <v>891.25</v>
       </c>
       <c r="C121" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>575</v>
       </c>
       <c r="D121" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>638.25</v>
       </c>
       <c r="E121" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>677.73393044726595</v>
       </c>
       <c r="F121" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>964.16</v>
       </c>
       <c r="G121" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>977.50000000000011</v>
       </c>
       <c r="H121" s="13">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>1026.0875000000001</v>
       </c>
       <c r="L121">
@@ -24685,7 +24725,7 @@
         <v>891.25</v>
       </c>
       <c r="C123" s="11">
-        <f t="shared" ref="C123" si="59">C118/C119</f>
+        <f t="shared" ref="C123" si="63">C118/C119</f>
         <v>575</v>
       </c>
       <c r="D123" s="11">
@@ -24693,19 +24733,19 @@
         <v>638.25</v>
       </c>
       <c r="E123" s="11">
-        <f t="shared" ref="E123:H123" si="60">E118/E119</f>
+        <f t="shared" ref="E123:H123" si="64">E118/E119</f>
         <v>677.73393044726595</v>
       </c>
       <c r="F123" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>964.16</v>
       </c>
       <c r="G123" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>977.50000000000011</v>
       </c>
       <c r="H123" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1026.0875000000001</v>
       </c>
     </row>
@@ -24740,7 +24780,7 @@
         <v>28</v>
       </c>
       <c r="B125" s="11">
-        <f t="shared" ref="B125" si="61">B118/B119</f>
+        <f t="shared" ref="B125" si="65">B118/B119</f>
         <v>891.25</v>
       </c>
       <c r="C125" s="11">
@@ -24748,11 +24788,11 @@
         <v>575</v>
       </c>
       <c r="D125" s="11">
-        <f t="shared" ref="D125:E125" si="62">D118/D119</f>
+        <f t="shared" ref="D125:E125" si="66">D118/D119</f>
         <v>638.25</v>
       </c>
       <c r="E125" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>677.73393044726595</v>
       </c>
       <c r="F125" s="11">
@@ -24760,7 +24800,7 @@
         <v>964.16</v>
       </c>
       <c r="G125" s="11">
-        <f t="shared" ref="G125" si="63">G118/G119</f>
+        <f t="shared" ref="G125" si="67">G118/G119</f>
         <v>977.50000000000011</v>
       </c>
       <c r="H125" s="11">
@@ -24803,7 +24843,7 @@
         <v>891.25</v>
       </c>
       <c r="C127" s="11">
-        <f t="shared" ref="C127" si="64">C118/C119</f>
+        <f t="shared" ref="C127" si="68">C118/C119</f>
         <v>575</v>
       </c>
       <c r="D127" s="11">
@@ -24811,19 +24851,19 @@
         <v>638.25</v>
       </c>
       <c r="E127" s="11">
-        <f t="shared" ref="E127:H127" si="65">E118/E119</f>
+        <f t="shared" ref="E127:H127" si="69">E118/E119</f>
         <v>677.73393044726595</v>
       </c>
       <c r="F127" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>964.16</v>
       </c>
       <c r="G127" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>977.50000000000011</v>
       </c>
       <c r="H127" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>1026.0875000000001</v>
       </c>
     </row>
@@ -24949,27 +24989,27 @@
         <v>8060</v>
       </c>
       <c r="C137" s="11">
-        <f t="shared" ref="C137:H137" si="66">$B$134*C135</f>
+        <f t="shared" ref="C137:H137" si="70">$B$134*C135</f>
         <v>5200</v>
       </c>
       <c r="D137" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>5772</v>
       </c>
       <c r="E137" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>6129.0720666535362</v>
       </c>
       <c r="F137" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>8719.36</v>
       </c>
       <c r="G137" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>8840</v>
       </c>
       <c r="H137" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>9279.4</v>
       </c>
     </row>
@@ -25047,31 +25087,31 @@
         <v>41</v>
       </c>
       <c r="B140" s="13">
-        <f t="shared" ref="B140:H140" si="67">B137/B138</f>
+        <f t="shared" ref="B140:H140" si="71">B137/B138</f>
         <v>2015</v>
       </c>
       <c r="C140" s="13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1300</v>
       </c>
       <c r="D140" s="13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1443</v>
       </c>
       <c r="E140" s="13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1532.2680166633841</v>
       </c>
       <c r="F140" s="13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>2179.84</v>
       </c>
       <c r="G140" s="13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>2210</v>
       </c>
       <c r="H140" s="13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>2319.85</v>
       </c>
     </row>
@@ -25108,7 +25148,7 @@
         <v>2015</v>
       </c>
       <c r="C142" s="11">
-        <f t="shared" ref="C142" si="68">C137/C138</f>
+        <f t="shared" ref="C142" si="72">C137/C138</f>
         <v>1300</v>
       </c>
       <c r="D142" s="11">
@@ -25116,19 +25156,19 @@
         <v>1443</v>
       </c>
       <c r="E142" s="11">
-        <f t="shared" ref="E142:H142" si="69">E137/E138</f>
+        <f t="shared" ref="E142:H142" si="73">E137/E138</f>
         <v>1532.2680166633841</v>
       </c>
       <c r="F142" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2179.84</v>
       </c>
       <c r="G142" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2210</v>
       </c>
       <c r="H142" s="11">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2319.85</v>
       </c>
     </row>
@@ -25163,7 +25203,7 @@
         <v>28</v>
       </c>
       <c r="B144" s="11">
-        <f t="shared" ref="B144" si="70">B137/B138</f>
+        <f t="shared" ref="B144" si="74">B137/B138</f>
         <v>2015</v>
       </c>
       <c r="C144" s="11">
@@ -25171,11 +25211,11 @@
         <v>1300</v>
       </c>
       <c r="D144" s="11">
-        <f t="shared" ref="D144:E144" si="71">D137/D138</f>
+        <f t="shared" ref="D144:E144" si="75">D137/D138</f>
         <v>1443</v>
       </c>
       <c r="E144" s="11">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>1532.2680166633841</v>
       </c>
       <c r="F144" s="11">
@@ -25183,7 +25223,7 @@
         <v>2179.84</v>
       </c>
       <c r="G144" s="11">
-        <f t="shared" ref="G144" si="72">G137/G138</f>
+        <f t="shared" ref="G144" si="76">G137/G138</f>
         <v>2210</v>
       </c>
       <c r="H144" s="11">
@@ -25226,7 +25266,7 @@
         <v>2015</v>
       </c>
       <c r="C146" s="11">
-        <f t="shared" ref="C146" si="73">C137/C138</f>
+        <f t="shared" ref="C146" si="77">C137/C138</f>
         <v>1300</v>
       </c>
       <c r="D146" s="11">
@@ -25234,19 +25274,19 @@
         <v>1443</v>
       </c>
       <c r="E146" s="11">
-        <f t="shared" ref="E146:H146" si="74">E137/E138</f>
+        <f t="shared" ref="E146:H146" si="78">E137/E138</f>
         <v>1532.2680166633841</v>
       </c>
       <c r="F146" s="11">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2179.84</v>
       </c>
       <c r="G146" s="11">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2210</v>
       </c>
       <c r="H146" s="11">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2319.85</v>
       </c>
     </row>
@@ -25372,27 +25412,27 @@
         <v>12988.841899999999</v>
       </c>
       <c r="C156" s="11">
-        <f t="shared" ref="C156:H156" si="75">$B$153*C154</f>
+        <f t="shared" ref="C156:H156" si="79">$B$153*C154</f>
         <v>8379.8979999999992</v>
       </c>
       <c r="D156" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>9301.68678</v>
       </c>
       <c r="E156" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>9877.1151448472756</v>
       </c>
       <c r="F156" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>14051.412966399999</v>
       </c>
       <c r="G156" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>14245.8266</v>
       </c>
       <c r="H156" s="11">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>14953.927980999999</v>
       </c>
     </row>
@@ -25449,31 +25489,31 @@
         <v>41</v>
       </c>
       <c r="B159" s="13">
-        <f t="shared" ref="B159:H159" si="76">B156/B157</f>
+        <f t="shared" ref="B159:H159" si="80">B156/B157</f>
         <v>3247.2104749999999</v>
       </c>
       <c r="C159" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>2094.9744999999998</v>
       </c>
       <c r="D159" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>2325.421695</v>
       </c>
       <c r="E159" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>2469.2787862118189</v>
       </c>
       <c r="F159" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>3512.8532415999998</v>
       </c>
       <c r="G159" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>3561.4566500000001</v>
       </c>
       <c r="H159" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>3738.4819952499997</v>
       </c>
       <c r="N159">
@@ -25531,7 +25571,7 @@
         <v>3247.2104749999999</v>
       </c>
       <c r="C161" s="11">
-        <f t="shared" ref="C161" si="77">C156/C157</f>
+        <f t="shared" ref="C161" si="81">C156/C157</f>
         <v>2094.9744999999998</v>
       </c>
       <c r="D161" s="11">
@@ -25539,19 +25579,19 @@
         <v>2325.421695</v>
       </c>
       <c r="E161" s="11">
-        <f t="shared" ref="E161:H161" si="78">E156/E157</f>
+        <f t="shared" ref="E161:H161" si="82">E156/E157</f>
         <v>2469.2787862118189</v>
       </c>
       <c r="F161" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>3512.8532415999998</v>
       </c>
       <c r="G161" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>3561.4566500000001</v>
       </c>
       <c r="H161" s="11">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>3738.4819952499997</v>
       </c>
     </row>
@@ -25589,7 +25629,7 @@
         <v>28</v>
       </c>
       <c r="B163" s="11">
-        <f t="shared" ref="B163" si="79">B156/B157</f>
+        <f t="shared" ref="B163" si="83">B156/B157</f>
         <v>3247.2104749999999</v>
       </c>
       <c r="C163" s="11">
@@ -25597,11 +25637,11 @@
         <v>2094.9744999999998</v>
       </c>
       <c r="D163" s="11">
-        <f t="shared" ref="D163:E163" si="80">D156/D157</f>
+        <f t="shared" ref="D163:E163" si="84">D156/D157</f>
         <v>2325.421695</v>
       </c>
       <c r="E163" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>2469.2787862118189</v>
       </c>
       <c r="F163" s="11">
@@ -25609,7 +25649,7 @@
         <v>3512.8532415999998</v>
       </c>
       <c r="G163" s="11">
-        <f t="shared" ref="G163" si="81">G156/G157</f>
+        <f t="shared" ref="G163" si="85">G156/G157</f>
         <v>3561.4566500000001</v>
       </c>
       <c r="H163" s="11">
@@ -25658,7 +25698,7 @@
         <v>3247.2104749999999</v>
       </c>
       <c r="C165" s="11">
-        <f t="shared" ref="C165" si="82">C156/C157</f>
+        <f t="shared" ref="C165" si="86">C156/C157</f>
         <v>2094.9744999999998</v>
       </c>
       <c r="D165" s="11">
@@ -25666,19 +25706,19 @@
         <v>2325.421695</v>
       </c>
       <c r="E165" s="11">
-        <f t="shared" ref="E165:H165" si="83">E156/E157</f>
+        <f t="shared" ref="E165:H165" si="87">E156/E157</f>
         <v>2469.2787862118189</v>
       </c>
       <c r="F165" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>3512.8532415999998</v>
       </c>
       <c r="G165" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>3561.4566500000001</v>
       </c>
       <c r="H165" s="11">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>3738.4819952499997</v>
       </c>
       <c r="N165">
@@ -25813,27 +25853,27 @@
       <c r="A175" s="10"/>
       <c r="B175" s="11"/>
       <c r="C175" s="11">
-        <f t="shared" ref="C175:H175" si="84">$B$172*C173</f>
+        <f t="shared" ref="C175:H175" si="88">$B$172*C173</f>
         <v>2947.0441000000001</v>
       </c>
       <c r="D175" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>3173.7398000000003</v>
       </c>
       <c r="E175" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>3287.0876499999999</v>
       </c>
       <c r="F175" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>4193.8704500000003</v>
       </c>
       <c r="G175" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>4420.5661499999997</v>
       </c>
       <c r="H175" s="11">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>4647.2618499999999</v>
       </c>
     </row>
@@ -25890,31 +25930,31 @@
         <v>41</v>
       </c>
       <c r="B178" s="13">
-        <f t="shared" ref="B178:H178" si="85">B175/B176</f>
+        <f t="shared" ref="B178:H178" si="89">B175/B176</f>
         <v>0</v>
       </c>
       <c r="C178" s="13">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>736.76102500000002</v>
       </c>
       <c r="D178" s="13">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>793.43495000000007</v>
       </c>
       <c r="E178" s="13">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>821.77191249999998</v>
       </c>
       <c r="F178" s="13">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1048.4676125000001</v>
       </c>
       <c r="G178" s="13">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1105.1415374999999</v>
       </c>
       <c r="H178" s="13">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1161.8154625</v>
       </c>
     </row>
@@ -25951,7 +25991,7 @@
         <v>0</v>
       </c>
       <c r="C180" s="11">
-        <f t="shared" ref="C180" si="86">C175/C176</f>
+        <f t="shared" ref="C180" si="90">C175/C176</f>
         <v>736.76102500000002</v>
       </c>
       <c r="D180" s="11">
@@ -25959,19 +25999,19 @@
         <v>793.43495000000007</v>
       </c>
       <c r="E180" s="11">
-        <f t="shared" ref="E180:H180" si="87">E175/E176</f>
+        <f t="shared" ref="E180:H180" si="91">E175/E176</f>
         <v>821.77191249999998</v>
       </c>
       <c r="F180" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>1048.4676125000001</v>
       </c>
       <c r="G180" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>1105.1415374999999</v>
       </c>
       <c r="H180" s="11">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>1161.8154625</v>
       </c>
       <c r="M180">
@@ -26024,7 +26064,7 @@
         <v>28</v>
       </c>
       <c r="B182" s="11">
-        <f t="shared" ref="B182" si="88">B175/B176</f>
+        <f t="shared" ref="B182" si="92">B175/B176</f>
         <v>0</v>
       </c>
       <c r="C182" s="11">
@@ -26032,11 +26072,11 @@
         <v>736.76102500000002</v>
       </c>
       <c r="D182" s="11">
-        <f t="shared" ref="D182:E182" si="89">D175/D176</f>
+        <f t="shared" ref="D182:E182" si="93">D175/D176</f>
         <v>793.43495000000007</v>
       </c>
       <c r="E182" s="11">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>821.77191249999998</v>
       </c>
       <c r="F182" s="11">
@@ -26044,7 +26084,7 @@
         <v>1048.4676125000001</v>
       </c>
       <c r="G182" s="11">
-        <f t="shared" ref="G182" si="90">G175/G176</f>
+        <f t="shared" ref="G182" si="94">G175/G176</f>
         <v>1105.1415374999999</v>
       </c>
       <c r="H182" s="11">
@@ -26093,7 +26133,7 @@
         <v>0</v>
       </c>
       <c r="C184" s="11">
-        <f t="shared" ref="C184" si="91">C175/C176</f>
+        <f t="shared" ref="C184" si="95">C175/C176</f>
         <v>736.76102500000002</v>
       </c>
       <c r="D184" s="11">
@@ -26101,19 +26141,19 @@
         <v>793.43495000000007</v>
       </c>
       <c r="E184" s="11">
-        <f t="shared" ref="E184:H184" si="92">E175/E176</f>
+        <f t="shared" ref="E184:H184" si="96">E175/E176</f>
         <v>821.77191249999998</v>
       </c>
       <c r="F184" s="11">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1048.4676125000001</v>
       </c>
       <c r="G184" s="11">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1105.1415374999999</v>
       </c>
       <c r="H184" s="11">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1161.8154625</v>
       </c>
       <c r="M184">
@@ -26252,23 +26292,23 @@
         <v>2836.6</v>
       </c>
       <c r="D194" s="11">
-        <f t="shared" ref="D194:H194" si="93">$B$191*D192</f>
+        <f t="shared" ref="D194:H194" si="97">$B$191*D192</f>
         <v>3054.8</v>
       </c>
       <c r="E194" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>3163.8999999999996</v>
       </c>
       <c r="F194" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>4036.7</v>
       </c>
       <c r="G194" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>4254.9000000000005</v>
       </c>
       <c r="H194" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>4473.0999999999995</v>
       </c>
     </row>
@@ -26325,31 +26365,31 @@
         <v>41</v>
       </c>
       <c r="B197" s="13">
-        <f t="shared" ref="B197:H197" si="94">B194/B195</f>
+        <f t="shared" ref="B197:H197" si="98">B194/B195</f>
         <v>0</v>
       </c>
       <c r="C197" s="13">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>709.15</v>
       </c>
       <c r="D197" s="13">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>763.7</v>
       </c>
       <c r="E197" s="13">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>790.97499999999991</v>
       </c>
       <c r="F197" s="13">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>1009.175</v>
       </c>
       <c r="G197" s="13">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>1063.7250000000001</v>
       </c>
       <c r="H197" s="13">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>1118.2749999999999</v>
       </c>
       <c r="L197">
@@ -26404,7 +26444,7 @@
         <v>0</v>
       </c>
       <c r="C199" s="11">
-        <f t="shared" ref="C199" si="95">C194/C195</f>
+        <f t="shared" ref="C199" si="99">C194/C195</f>
         <v>709.15</v>
       </c>
       <c r="D199" s="11">
@@ -26412,19 +26452,19 @@
         <v>763.7</v>
       </c>
       <c r="E199" s="11">
-        <f t="shared" ref="E199:H199" si="96">E194/E195</f>
+        <f t="shared" ref="E199:H199" si="100">E194/E195</f>
         <v>790.97499999999991</v>
       </c>
       <c r="F199" s="11">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>1009.175</v>
       </c>
       <c r="G199" s="11">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>1063.7250000000001</v>
       </c>
       <c r="H199" s="11">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>1118.2749999999999</v>
       </c>
       <c r="L199">
@@ -26471,7 +26511,7 @@
         <v>28</v>
       </c>
       <c r="B201" s="11">
-        <f t="shared" ref="B201" si="97">B194/B195</f>
+        <f t="shared" ref="B201" si="101">B194/B195</f>
         <v>0</v>
       </c>
       <c r="C201" s="11">
@@ -26479,11 +26519,11 @@
         <v>709.15</v>
       </c>
       <c r="D201" s="11">
-        <f t="shared" ref="D201:E201" si="98">D194/D195</f>
+        <f t="shared" ref="D201:E201" si="102">D194/D195</f>
         <v>763.7</v>
       </c>
       <c r="E201" s="11">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>790.97499999999991</v>
       </c>
       <c r="F201" s="11">
@@ -26491,7 +26531,7 @@
         <v>1009.175</v>
       </c>
       <c r="G201" s="11">
-        <f t="shared" ref="G201" si="99">G194/G195</f>
+        <f t="shared" ref="G201" si="103">G194/G195</f>
         <v>1063.7250000000001</v>
       </c>
       <c r="H201" s="11">
@@ -26546,7 +26586,7 @@
         <v>0</v>
       </c>
       <c r="C203" s="11">
-        <f t="shared" ref="C203" si="100">C194/C195</f>
+        <f t="shared" ref="C203" si="104">C194/C195</f>
         <v>709.15</v>
       </c>
       <c r="D203" s="11">
@@ -26554,19 +26594,19 @@
         <v>763.7</v>
       </c>
       <c r="E203" s="11">
-        <f t="shared" ref="E203:H203" si="101">E194/E195</f>
+        <f t="shared" ref="E203:H203" si="105">E194/E195</f>
         <v>790.97499999999991</v>
       </c>
       <c r="F203" s="11">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>1009.175</v>
       </c>
       <c r="G203" s="11">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>1063.7250000000001</v>
       </c>
       <c r="H203" s="11">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>1118.2749999999999</v>
       </c>
       <c r="L203">
@@ -26705,23 +26745,23 @@
         <v>4788.4759000000004</v>
       </c>
       <c r="D213" s="11">
-        <f t="shared" ref="D213:H213" si="102">$B$210*D211</f>
+        <f t="shared" ref="D213:H213" si="106">$B$210*D211</f>
         <v>5156.8202000000001</v>
       </c>
       <c r="E213" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>5340.9923499999995</v>
       </c>
       <c r="F213" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>6814.3695500000003</v>
       </c>
       <c r="G213" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>7182.7138500000001</v>
       </c>
       <c r="H213" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>7551.0581499999998</v>
       </c>
     </row>
@@ -26799,31 +26839,31 @@
         <v>41</v>
       </c>
       <c r="B216" s="13">
-        <f t="shared" ref="B216:H216" si="103">B213/B214</f>
+        <f t="shared" ref="B216:H216" si="107">B213/B214</f>
         <v>0</v>
       </c>
       <c r="C216" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>1197.1189750000001</v>
       </c>
       <c r="D216" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>1289.20505</v>
       </c>
       <c r="E216" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>1335.2480874999999</v>
       </c>
       <c r="F216" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>1703.5923875000001</v>
       </c>
       <c r="G216" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>1795.6784625</v>
       </c>
       <c r="H216" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>1887.7645375</v>
       </c>
       <c r="M216">
@@ -26866,7 +26906,7 @@
         <v>0</v>
       </c>
       <c r="C218" s="11">
-        <f t="shared" ref="C218" si="104">C213/C214</f>
+        <f t="shared" ref="C218" si="108">C213/C214</f>
         <v>1197.1189750000001</v>
       </c>
       <c r="D218" s="11">
@@ -26874,19 +26914,19 @@
         <v>1289.20505</v>
       </c>
       <c r="E218" s="11">
-        <f t="shared" ref="E218:H218" si="105">E213/E214</f>
+        <f t="shared" ref="E218:H218" si="109">E213/E214</f>
         <v>1335.2480874999999</v>
       </c>
       <c r="F218" s="11">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>1703.5923875000001</v>
       </c>
       <c r="G218" s="11">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>1795.6784625</v>
       </c>
       <c r="H218" s="11">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>1887.7645375</v>
       </c>
       <c r="M218">
@@ -26927,7 +26967,7 @@
         <v>28</v>
       </c>
       <c r="B220" s="11">
-        <f t="shared" ref="B220" si="106">B213/B214</f>
+        <f t="shared" ref="B220" si="110">B213/B214</f>
         <v>0</v>
       </c>
       <c r="C220" s="11">
@@ -26935,11 +26975,11 @@
         <v>1197.1189750000001</v>
       </c>
       <c r="D220" s="11">
-        <f t="shared" ref="D220:E220" si="107">D213/D214</f>
+        <f t="shared" ref="D220:E220" si="111">D213/D214</f>
         <v>1289.20505</v>
       </c>
       <c r="E220" s="11">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>1335.2480874999999</v>
       </c>
       <c r="F220" s="11">
@@ -26947,7 +26987,7 @@
         <v>1703.5923875000001</v>
       </c>
       <c r="G220" s="11">
-        <f t="shared" ref="G220" si="108">G213/G214</f>
+        <f t="shared" ref="G220" si="112">G213/G214</f>
         <v>1795.6784625</v>
       </c>
       <c r="H220" s="11">
@@ -26993,7 +27033,7 @@
         <v>0</v>
       </c>
       <c r="C222" s="11">
-        <f t="shared" ref="C222" si="109">C213/C214</f>
+        <f t="shared" ref="C222" si="113">C213/C214</f>
         <v>1197.1189750000001</v>
       </c>
       <c r="D222" s="11">
@@ -27001,19 +27041,19 @@
         <v>1289.20505</v>
       </c>
       <c r="E222" s="11">
-        <f t="shared" ref="E222:H222" si="110">E213/E214</f>
+        <f t="shared" ref="E222:H222" si="114">E213/E214</f>
         <v>1335.2480874999999</v>
       </c>
       <c r="F222" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>1703.5923875000001</v>
       </c>
       <c r="G222" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>1795.6784625</v>
       </c>
       <c r="H222" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>1887.7645375</v>
       </c>
     </row>
@@ -27166,23 +27206,23 @@
         <v>1850.03</v>
       </c>
       <c r="D232" s="11">
-        <f t="shared" ref="D232:H232" si="111">$B$229*D230</f>
+        <f t="shared" ref="D232:H232" si="115">$B$229*D230</f>
         <v>1992.3400000000001</v>
       </c>
       <c r="E232" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>2063.4949999999999</v>
       </c>
       <c r="F232" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>2632.7350000000001</v>
       </c>
       <c r="G232" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>2775.0450000000001</v>
       </c>
       <c r="H232" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>2917.355</v>
       </c>
       <c r="M232">
@@ -27248,31 +27288,31 @@
         <v>41</v>
       </c>
       <c r="B235" s="13">
-        <f t="shared" ref="B235:H235" si="112">B232/B233</f>
+        <f t="shared" ref="B235:H235" si="116">B232/B233</f>
         <v>0</v>
       </c>
       <c r="C235" s="13">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>462.50749999999999</v>
       </c>
       <c r="D235" s="13">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>498.08500000000004</v>
       </c>
       <c r="E235" s="13">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>515.87374999999997</v>
       </c>
       <c r="F235" s="13">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>658.18375000000003</v>
       </c>
       <c r="G235" s="13">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>693.76125000000002</v>
       </c>
       <c r="H235" s="13">
-        <f t="shared" si="112"/>
+        <f t="shared" si="116"/>
         <v>729.33875</v>
       </c>
       <c r="M235">
@@ -27312,7 +27352,7 @@
         <v>0</v>
       </c>
       <c r="C237" s="11">
-        <f t="shared" ref="C237" si="113">C232/C233</f>
+        <f t="shared" ref="C237" si="117">C232/C233</f>
         <v>462.50749999999999</v>
       </c>
       <c r="D237" s="11">
@@ -27320,19 +27360,19 @@
         <v>498.08500000000004</v>
       </c>
       <c r="E237" s="11">
-        <f t="shared" ref="E237:H237" si="114">E232/E233</f>
+        <f t="shared" ref="E237:H237" si="118">E232/E233</f>
         <v>515.87374999999997</v>
       </c>
       <c r="F237" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>658.18375000000003</v>
       </c>
       <c r="G237" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>693.76125000000002</v>
       </c>
       <c r="H237" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="118"/>
         <v>729.33875</v>
       </c>
     </row>
@@ -27367,7 +27407,7 @@
         <v>28</v>
       </c>
       <c r="B239" s="11">
-        <f t="shared" ref="B239" si="115">B232/B233</f>
+        <f t="shared" ref="B239" si="119">B232/B233</f>
         <v>0</v>
       </c>
       <c r="C239" s="11">
@@ -27375,11 +27415,11 @@
         <v>462.50749999999999</v>
       </c>
       <c r="D239" s="11">
-        <f t="shared" ref="D239:E239" si="116">D232/D233</f>
+        <f t="shared" ref="D239:E239" si="120">D232/D233</f>
         <v>498.08500000000004</v>
       </c>
       <c r="E239" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="120"/>
         <v>515.87374999999997</v>
       </c>
       <c r="F239" s="11">
@@ -27387,7 +27427,7 @@
         <v>658.18375000000003</v>
       </c>
       <c r="G239" s="11">
-        <f t="shared" ref="G239" si="117">G232/G233</f>
+        <f t="shared" ref="G239" si="121">G232/G233</f>
         <v>693.76125000000002</v>
       </c>
       <c r="H239" s="11">
@@ -27430,7 +27470,7 @@
         <v>0</v>
       </c>
       <c r="C241" s="11">
-        <f t="shared" ref="C241" si="118">C232/C233</f>
+        <f t="shared" ref="C241" si="122">C232/C233</f>
         <v>462.50749999999999</v>
       </c>
       <c r="D241" s="11">
@@ -27438,19 +27478,19 @@
         <v>498.08500000000004</v>
       </c>
       <c r="E241" s="11">
-        <f t="shared" ref="E241:H241" si="119">E232/E233</f>
+        <f t="shared" ref="E241:H241" si="123">E232/E233</f>
         <v>515.87374999999997</v>
       </c>
       <c r="F241" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>658.18375000000003</v>
       </c>
       <c r="G241" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>693.76125000000002</v>
       </c>
       <c r="H241" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>729.33875</v>
       </c>
     </row>
@@ -27509,6 +27549,23 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C96:H96"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="C153:H153"/>
     <mergeCell ref="C210:H210"/>
     <mergeCell ref="A216:A217"/>
     <mergeCell ref="C229:H229"/>
@@ -27518,23 +27575,6 @@
     <mergeCell ref="A178:A179"/>
     <mergeCell ref="C191:H191"/>
     <mergeCell ref="A197:A198"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="C153:H153"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C96:H96"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="A64:A65"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -28183,15 +28223,15 @@
   </cols>
   <sheetData>
     <row r="5" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="G5" s="73" t="s">
+      <c r="E5" s="72"/>
+      <c r="G5" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
     </row>
     <row r="6" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D6" s="27" t="s">
@@ -28298,15 +28338,15 @@
       </c>
     </row>
     <row r="13" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D14" s="27" t="s">
@@ -28447,17 +28487,17 @@
       </c>
     </row>
     <row r="21" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D21" s="73" t="s">
+      <c r="D21" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="73"/>
-      <c r="K21" s="73"/>
-      <c r="L21" s="73"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
     </row>
     <row r="22" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D22" s="27" t="s">
